--- a/astro-site/public/dl/plan-negocio-taqueria/plan-financiero-taqueria.xlsx
+++ b/astro-site/public/dl/plan-negocio-taqueria/plan-financiero-taqueria.xlsx
@@ -7125,7 +7125,7 @@
       </c>
       <c r="D37" s="48" t="inlineStr">
         <is>
-          <t>Tortilla, 35 g de carne servida, piña, cebolla, cilantro, lima y salsa, con un 5 % de merma. La carne y la tortilla no tienen precio profesional publicado: pon los de tu proveedor</t>
+          <t>Tortilla, 35 g de carne servida, piña, cebolla, cilantro, lima y salsa, con un 5 % de merma. La carne y la tortilla son precios estimados por el kit: pon los de tu proveedor</t>
         </is>
       </c>
       <c r="E37" s="29" t="n"/>
@@ -7778,7 +7778,7 @@
       </c>
       <c r="O5" s="29" t="inlineStr">
         <is>
-          <t>Mes 1 = ENERO, en el orden del calendario: enero y agosto son los meses más flojos y los picos llegan en septiembre (Independencia de México, 15 y 16), noviembre (Día de Muertos) y diciembre. Si abres en otro mes, gira la fila. Tiene que sumar 100 %</t>
+          <t>Mes 1 = ENERO, en el orden del calendario: enero y agosto son los meses más flojos, diciembre es el pico y septiembre (Independencia de México, 15 y 16) y noviembre (Día de Muertos) traen las fechas mexicanas. Si abres en otro mes, gira la fila. Tiene que sumar 100 %</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/plan-negocio-taqueria/plan-financiero-taqueria.xlsx
+++ b/astro-site/public/dl/plan-negocio-taqueria/plan-financiero-taqueria.xlsx
@@ -1583,7 +1583,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de entrar en pérdidas</t>
+          <t>Cuánto deben superar las ventas previstas a las del punto de equilibrio. La caída que aguantas antes de entrar en pérdidas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>
@@ -2235,7 +2235,7 @@
         <v>0.032119167010264495</v>
       </c>
       <c r="D27" s="29" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico de actividad y de salida de humos, y dirección de obra, Obra y acondicionamiento del local, rótulo y fachada, Conducto de extracción exclusivo hasta cubierta, Instalación eléctrica, cuadro y boletín y Fontanería, separador de grasas, climatización e instalación de gas), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico de actividad y de salida de humos, y dirección de obra, Obra y acondicionamiento del local, rótulo y fachada, Conducto de extracción exclusivo hasta cubierta, "&amp;"Instalación eléctrica, cuadro y boletín y Fontanería, separador de grasas, climatización e instalación de gas), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje "&amp;"está en la hoja de Supuestos","")</f>
         <v>Al 10% de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico de actividad y de salida de humos, y dirección de obra, Obra y acondicionamiento del local, rótulo y fachada, Conducto de extracción exclusivo hasta cubierta, Instalación eléctrica, cuadro y boletín y Fontanería, separador de grasas, climatización e instalación de gas), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos</v>
       </c>
       <c r="E27" s="29" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="C32" s="29" t="n"/>
       <c r="D32" s="29" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí "&amp;"(21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
         <v>Al 21% sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo</v>
       </c>
       <c r="E32" s="29" t="n"/>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="C37" s="29" t="n"/>
       <c r="D37" s="26" t="str">
-        <f>IFERROR("No se amortizan, por no ser inmovilizado, Constitución de la SL, licencia, tasas, registro sanitario y APPCC, Marca, web, fotos y lanzamiento, Stock inicial: carnes, chiles, tortillas, bebida y envases, Fianza del alquiler, Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B30-B35-B36,"0")&amp;" € de los "&amp;TEXT(B30,"0")&amp;" € de inversión.","")</f>
+        <f>IFERROR("No se amortizan, por no ser inmovilizado, Constitución de la SL, licencia, tasas, registro sanitario y APPCC, Marca, web, fotos y lanzamiento, Stock inicial: carnes, chiles, tortillas, bebida y envases, Fianza del alquiler, Alquiler de los "&amp;"meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B30-B35-B36,"0")&amp;" € de los "&amp;TEXT(B30,"0")&amp;" € de inversión.","")</f>
         <v>No se amortizan, por no ser inmovilizado, Constitución de la SL, licencia, tasas, registro sanitario y APPCC, Marca, web, fotos y lanzamiento, Stock inicial: carnes, chiles, tortillas, bebida y envases, Fianza del alquiler, Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman 61650 € de los 151000 € de inversión.</v>
       </c>
       <c r="E37" s="29" t="n"/>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="E24" s="29" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer antes de no poder pagar los costes fijos y la cuota. El mínimo exigible está en la hoja de Supuestos</t>
+          <t>Cuánto superan tus ventas previstas a las del equilibrio de caja. La caída que aguantas antes de no poder pagar los costes fijos y la cuota es algo menor: con un 25 % de holgura, un 20 %. El mínimo exigible está en la hoja de Supuestos</t>
         </is>
       </c>
       <c r="F24" s="29" t="n"/>

--- a/astro-site/public/dl/plan-negocio-taqueria/plan-financiero-taqueria.xlsx
+++ b/astro-site/public/dl/plan-negocio-taqueria/plan-financiero-taqueria.xlsx
@@ -1583,7 +1583,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto deben superar las ventas previstas a las del punto de equilibrio. La caída que aguantas antes de entrar en pérdidas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
+          <t>Cuánto deben superar las ventas previstas a las del equilibrio de caja (costes fijos y cuota del préstamo). La caída que aguantas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/plan-negocio-taqueria/plan-financiero-taqueria.xlsx
+++ b/astro-site/public/dl/plan-negocio-taqueria/plan-financiero-taqueria.xlsx
@@ -1583,7 +1583,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de entrar en pérdidas</t>
+          <t>Cuánto deben superar las ventas previstas a las del equilibrio de caja (costes fijos y cuota del préstamo). La caída que aguantas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>
@@ -2235,7 +2235,7 @@
         <v>0.032119167010264495</v>
       </c>
       <c r="D27" s="29" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico de actividad y de salida de humos, y dirección de obra, Obra y acondicionamiento del local, rótulo y fachada, Conducto de extracción exclusivo hasta cubierta, Instalación eléctrica, cuadro y boletín y Fontanería, separador de grasas, climatización e instalación de gas), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico de actividad y de salida de humos, y dirección de obra, Obra y acondicionamiento del local, rótulo y fachada, Conducto de extracción exclusivo hasta cubierta, "&amp;"Instalación eléctrica, cuadro y boletín y Fontanería, separador de grasas, climatización e instalación de gas), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje "&amp;"está en la hoja de Supuestos","")</f>
         <v>Al 10% de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico de actividad y de salida de humos, y dirección de obra, Obra y acondicionamiento del local, rótulo y fachada, Conducto de extracción exclusivo hasta cubierta, Instalación eléctrica, cuadro y boletín y Fontanería, separador de grasas, climatización e instalación de gas), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos</v>
       </c>
       <c r="E27" s="29" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="C32" s="29" t="n"/>
       <c r="D32" s="29" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí "&amp;"(21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
         <v>Al 21% sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo</v>
       </c>
       <c r="E32" s="29" t="n"/>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="C37" s="29" t="n"/>
       <c r="D37" s="26" t="str">
-        <f>IFERROR("No se amortizan, por no ser inmovilizado, Constitución de la SL, licencia, tasas, registro sanitario y APPCC, Marca, web, fotos y lanzamiento, Stock inicial: carnes, chiles, tortillas, bebida y envases, Fianza del alquiler, Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B30-B35-B36,"0")&amp;" € de los "&amp;TEXT(B30,"0")&amp;" € de inversión.","")</f>
+        <f>IFERROR("No se amortizan, por no ser inmovilizado, Constitución de la SL, licencia, tasas, registro sanitario y APPCC, Marca, web, fotos y lanzamiento, Stock inicial: carnes, chiles, tortillas, bebida y envases, Fianza del alquiler, Alquiler de los "&amp;"meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B30-B35-B36,"0")&amp;" € de los "&amp;TEXT(B30,"0")&amp;" € de inversión.","")</f>
         <v>No se amortizan, por no ser inmovilizado, Constitución de la SL, licencia, tasas, registro sanitario y APPCC, Marca, web, fotos y lanzamiento, Stock inicial: carnes, chiles, tortillas, bebida y envases, Fianza del alquiler, Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman 61650 € de los 151000 € de inversión.</v>
       </c>
       <c r="E37" s="29" t="n"/>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="E24" s="29" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer antes de no poder pagar los costes fijos y la cuota. El mínimo exigible está en la hoja de Supuestos</t>
+          <t>Cuánto superan tus ventas previstas a las del equilibrio de caja. La caída que aguantas antes de no poder pagar los costes fijos y la cuota es algo menor: con un 25 % de holgura, un 20 %. El mínimo exigible está en la hoja de Supuestos</t>
         </is>
       </c>
       <c r="F24" s="29" t="n"/>
